--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B3B457-4381-494E-9031-F18CEBC77A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A1A012-40F6-405D-93A7-C8CE583D3812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="190">
   <si>
     <t>Part Number</t>
   </si>
@@ -619,6 +619,18 @@
   </si>
   <si>
     <t>LP2951ACDG 8-SOIC</t>
+  </si>
+  <si>
+    <t>LM2776</t>
+  </si>
+  <si>
+    <t>SuperSOT6</t>
+  </si>
+  <si>
+    <t>LM2776DBVR</t>
+  </si>
+  <si>
+    <t>LM2776DBVR SuperSOT6</t>
   </si>
 </sst>
 </file>
@@ -674,14 +686,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
@@ -1217,7 +1228,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
@@ -1463,25 +1474,48 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="4" t="s">
+      <c r="A11" t="s">
         <v>184</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" t="s">
         <v>183</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" t="s">
         <v>184</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" t="s">
         <v>182</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B12" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E12" t="s">
+        <v>186</v>
+      </c>
+      <c r="F12" t="s">
+        <v>187</v>
+      </c>
+      <c r="G12" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2309,16 +2343,16 @@
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="4" t="s">
+      <c r="A31" t="s">
         <v>179</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" t="s">
         <v>185</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" t="s">
         <v>179</v>
       </c>
       <c r="E31" t="s">

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A1A012-40F6-405D-93A7-C8CE583D3812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D05957-1FC0-4F72-868B-B80D1989EBEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="195">
   <si>
     <t>Part Number</t>
   </si>
@@ -631,6 +631,21 @@
   </si>
   <si>
     <t>LM2776DBVR SuperSOT6</t>
+  </si>
+  <si>
+    <t>SOT23</t>
+  </si>
+  <si>
+    <t>XC6206P122</t>
+  </si>
+  <si>
+    <t>XC6206P122 SOT23</t>
+  </si>
+  <si>
+    <t>Torex</t>
+  </si>
+  <si>
+    <t>XC6206P</t>
   </si>
 </sst>
 </file>
@@ -1638,7 +1653,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
@@ -2363,6 +2378,29 @@
       </c>
       <c r="G31" t="s">
         <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>191</v>
+      </c>
+      <c r="B32" t="s">
+        <v>190</v>
+      </c>
+      <c r="C32" t="s">
+        <v>192</v>
+      </c>
+      <c r="D32" t="s">
+        <v>191</v>
+      </c>
+      <c r="E32" t="s">
+        <v>194</v>
+      </c>
+      <c r="F32" t="s">
+        <v>190</v>
+      </c>
+      <c r="G32" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D05957-1FC0-4F72-868B-B80D1989EBEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629ACEFF-6556-4EC4-8994-D57732D60498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="198">
   <si>
     <t>Part Number</t>
   </si>
@@ -646,6 +646,15 @@
   </si>
   <si>
     <t>XC6206P</t>
+  </si>
+  <si>
+    <t>IRM-10-12</t>
+  </si>
+  <si>
+    <t>TEN 5-1211</t>
+  </si>
+  <si>
+    <t>TRACO POWER</t>
   </si>
 </sst>
 </file>
@@ -1023,10 +1032,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1075,6 +1090,29 @@
         <v>13</v>
       </c>
       <c r="G2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1243,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
@@ -1532,6 +1570,29 @@
       </c>
       <c r="G12" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>196</v>
+      </c>
+      <c r="B13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C13" t="s">
+        <v>196</v>
+      </c>
+      <c r="D13" t="s">
+        <v>196</v>
+      </c>
+      <c r="E13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F13" t="s">
+        <v>196</v>
+      </c>
+      <c r="G13" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629ACEFF-6556-4EC4-8994-D57732D60498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872D2314-E03E-4AC4-BF80-73F352369F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="misc" sheetId="6" r:id="rId6"/>
     <sheet name="power_mux" sheetId="7" r:id="rId7"/>
     <sheet name="power_switch" sheetId="8" r:id="rId8"/>
+    <sheet name="Vref_sourse" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="201">
   <si>
     <t>Part Number</t>
   </si>
@@ -655,6 +656,15 @@
   </si>
   <si>
     <t>TRACO POWER</t>
+  </si>
+  <si>
+    <t>AD1582ARTZ</t>
+  </si>
+  <si>
+    <t>AD1582ARTZ SOT23</t>
+  </si>
+  <si>
+    <t>AD158x</t>
   </si>
 </sst>
 </file>
@@ -2802,4 +2812,71 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F703D42-6E7A-4C3C-A172-8A9EBFFB14A6}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872D2314-E03E-4AC4-BF80-73F352369F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D3EBD6-B37A-40AA-AEB3-8BA8D4C36B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="217">
   <si>
     <t>Part Number</t>
   </si>
@@ -666,12 +666,138 @@
   <si>
     <t>AD158x</t>
   </si>
+  <si>
+    <t>L79Lxx</t>
+  </si>
+  <si>
+    <t>L79L05ABUTR</t>
+  </si>
+  <si>
+    <t>SOT89</t>
+  </si>
+  <si>
+    <t>L79L05ABUTR SOT89</t>
+  </si>
+  <si>
+    <t>STMicroelectronics</t>
+  </si>
+  <si>
+    <t>LT8330</t>
+  </si>
+  <si>
+    <r>
+      <t>LT8330</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t>HS6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LT8330</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t>HS6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> SOT23-6</t>
+    </r>
+  </si>
+  <si>
+    <t>MIC29502</t>
+  </si>
+  <si>
+    <t>TO-263-6</t>
+  </si>
+  <si>
+    <t>Microchip</t>
+  </si>
+  <si>
+    <t>TPS61175</t>
+  </si>
+  <si>
+    <r>
+      <t>MIC29502</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t>WU</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TPS61175</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PWP</t>
+    </r>
+  </si>
+  <si>
+    <t>14-TSOP-EP</t>
+  </si>
+  <si>
+    <r>
+      <t>TPS61175</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PWP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 14-TSOP-EP</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -691,6 +817,14 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Inter"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -720,13 +854,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
@@ -1291,7 +1426,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
@@ -1603,6 +1738,29 @@
       </c>
       <c r="G13" t="s">
         <v>197</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B14" t="s">
+        <v>215</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="E14" t="s">
+        <v>212</v>
+      </c>
+      <c r="F14" t="s">
+        <v>215</v>
+      </c>
+      <c r="G14" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1724,7 +1882,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
@@ -2472,6 +2630,75 @@
       </c>
       <c r="G32" t="s">
         <v>193</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>202</v>
+      </c>
+      <c r="B33" t="s">
+        <v>203</v>
+      </c>
+      <c r="C33" t="s">
+        <v>204</v>
+      </c>
+      <c r="D33" t="s">
+        <v>202</v>
+      </c>
+      <c r="E33" t="s">
+        <v>201</v>
+      </c>
+      <c r="F33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G33" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E34" t="s">
+        <v>206</v>
+      </c>
+      <c r="F34" t="s">
+        <v>36</v>
+      </c>
+      <c r="G34" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B35" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35" t="s">
+        <v>209</v>
+      </c>
+      <c r="D35" t="s">
+        <v>209</v>
+      </c>
+      <c r="E35" t="s">
+        <v>209</v>
+      </c>
+      <c r="F35" t="s">
+        <v>210</v>
+      </c>
+      <c r="G35" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D3EBD6-B37A-40AA-AEB3-8BA8D4C36B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB03B1D-8684-4D83-9652-5075F7F72B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="218">
   <si>
     <t>Part Number</t>
   </si>
@@ -790,6 +790,22 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 14-TSOP-EP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LT8330</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HS6</t>
     </r>
   </si>
 </sst>
@@ -854,14 +870,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
@@ -1741,16 +1756,16 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="4" t="s">
+      <c r="A14" t="s">
         <v>214</v>
       </c>
       <c r="B14" t="s">
         <v>215</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" t="s">
         <v>216</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" t="s">
         <v>214</v>
       </c>
       <c r="E14" t="s">
@@ -2656,17 +2671,17 @@
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="4" t="s">
+      <c r="A34" t="s">
         <v>207</v>
       </c>
       <c r="B34" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" t="s">
         <v>208</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>207</v>
+      <c r="D34" t="s">
+        <v>217</v>
       </c>
       <c r="E34" t="s">
         <v>206</v>
@@ -2679,7 +2694,7 @@
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="4" t="s">
+      <c r="A35" t="s">
         <v>213</v>
       </c>
       <c r="B35" t="s">

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB03B1D-8684-4D83-9652-5075F7F72B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE1AB11-5223-429C-89B7-016A8FA8FCE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -1441,7 +1441,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
@@ -1776,6 +1776,29 @@
       </c>
       <c r="G14" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
+        <v>208</v>
+      </c>
+      <c r="D15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E15" t="s">
+        <v>206</v>
+      </c>
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -1897,7 +1920,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
@@ -2672,47 +2695,24 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>210</v>
       </c>
       <c r="C34" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D34" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E34" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F34" t="s">
-        <v>36</v>
+        <v>210</v>
       </c>
       <c r="G34" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" t="s">
-        <v>213</v>
-      </c>
-      <c r="B35" t="s">
-        <v>210</v>
-      </c>
-      <c r="C35" t="s">
-        <v>209</v>
-      </c>
-      <c r="D35" t="s">
-        <v>209</v>
-      </c>
-      <c r="E35" t="s">
-        <v>209</v>
-      </c>
-      <c r="F35" t="s">
-        <v>210</v>
-      </c>
-      <c r="G35" t="s">
         <v>211</v>
       </c>
     </row>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE1AB11-5223-429C-89B7-016A8FA8FCE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CAF751-9357-4B3F-86B0-152059D1F1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="220">
   <si>
     <t>Part Number</t>
   </si>
@@ -807,6 +807,12 @@
       </rPr>
       <t>HS6</t>
     </r>
+  </si>
+  <si>
+    <t>142ЕН12</t>
+  </si>
+  <si>
+    <t>бКО.347.098-11 ТУ</t>
   </si>
 </sst>
 </file>
@@ -1920,7 +1926,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
@@ -2670,7 +2676,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
         <v>202</v>
       </c>
@@ -2693,7 +2699,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
         <v>213</v>
       </c>
@@ -2714,6 +2720,29 @@
       </c>
       <c r="G34" t="s">
         <v>211</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>218</v>
+      </c>
+      <c r="B35" t="s">
+        <v>218</v>
+      </c>
+      <c r="C35" t="s">
+        <v>218</v>
+      </c>
+      <c r="D35" t="s">
+        <v>218</v>
+      </c>
+      <c r="E35" t="s">
+        <v>218</v>
+      </c>
+      <c r="F35" t="s">
+        <v>218</v>
+      </c>
+      <c r="H35" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CAF751-9357-4B3F-86B0-152059D1F1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D825D43-9F90-4DD1-8CAE-49BC58B2B8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="223">
   <si>
     <t>Part Number</t>
   </si>
@@ -813,6 +813,15 @@
   </si>
   <si>
     <t>бКО.347.098-11 ТУ</t>
+  </si>
+  <si>
+    <t>TO-263-3</t>
+  </si>
+  <si>
+    <t>LM1117SX-5.0</t>
+  </si>
+  <si>
+    <t>LM1117SX-5.0 TO-263-3</t>
   </si>
 </sst>
 </file>
@@ -1926,7 +1935,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
@@ -2743,6 +2752,29 @@
       </c>
       <c r="H35" t="s">
         <v>219</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>221</v>
+      </c>
+      <c r="B36" t="s">
+        <v>220</v>
+      </c>
+      <c r="C36" t="s">
+        <v>222</v>
+      </c>
+      <c r="D36" t="s">
+        <v>221</v>
+      </c>
+      <c r="E36" t="s">
+        <v>40</v>
+      </c>
+      <c r="F36" t="s">
+        <v>220</v>
+      </c>
+      <c r="G36" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D825D43-9F90-4DD1-8CAE-49BC58B2B8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914DD0F1-C6CD-4507-A119-EDAF4BF9A734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="227">
   <si>
     <t>Part Number</t>
   </si>
@@ -822,6 +822,18 @@
   </si>
   <si>
     <t>LM1117SX-5.0 TO-263-3</t>
+  </si>
+  <si>
+    <t>HRP5</t>
+  </si>
+  <si>
+    <t>BD00FDAWHFP</t>
+  </si>
+  <si>
+    <t>BD00FDAWHFP HRP5</t>
+  </si>
+  <si>
+    <t>ROHM</t>
   </si>
 </sst>
 </file>
@@ -1935,7 +1947,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
@@ -2775,6 +2787,29 @@
       </c>
       <c r="G36" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>224</v>
+      </c>
+      <c r="B37" t="s">
+        <v>223</v>
+      </c>
+      <c r="C37" t="s">
+        <v>225</v>
+      </c>
+      <c r="D37" t="s">
+        <v>224</v>
+      </c>
+      <c r="E37" t="s">
+        <v>224</v>
+      </c>
+      <c r="F37" t="s">
+        <v>223</v>
+      </c>
+      <c r="G37" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914DD0F1-C6CD-4507-A119-EDAF4BF9A734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8EC918-75E5-421B-9C7C-EF7CA3BBBA2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="2670" yWindow="1920" windowWidth="23085" windowHeight="13635" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="232">
   <si>
     <t>Part Number</t>
   </si>
@@ -834,6 +834,21 @@
   </si>
   <si>
     <t>ROHM</t>
+  </si>
+  <si>
+    <t>LT3093EMSE</t>
+  </si>
+  <si>
+    <t>12-MSOP (PAD)</t>
+  </si>
+  <si>
+    <t>12-MSOP</t>
+  </si>
+  <si>
+    <t>LT3093EMSE 12-MSOP</t>
+  </si>
+  <si>
+    <t>LT3093</t>
   </si>
 </sst>
 </file>
@@ -1947,7 +1962,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
@@ -2810,6 +2825,29 @@
       </c>
       <c r="G37" t="s">
         <v>226</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>227</v>
+      </c>
+      <c r="B38" t="s">
+        <v>229</v>
+      </c>
+      <c r="C38" t="s">
+        <v>230</v>
+      </c>
+      <c r="D38" t="s">
+        <v>227</v>
+      </c>
+      <c r="E38" t="s">
+        <v>231</v>
+      </c>
+      <c r="F38" t="s">
+        <v>228</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8EC918-75E5-421B-9C7C-EF7CA3BBBA2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193CE901-EAE1-4122-8B24-4FFF06B34291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2670" yWindow="1920" windowWidth="23085" windowHeight="13635" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="2670" yWindow="1920" windowWidth="23085" windowHeight="13635" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="235">
   <si>
     <t>Part Number</t>
   </si>
@@ -849,6 +849,15 @@
   </si>
   <si>
     <t>LT3093</t>
+  </si>
+  <si>
+    <t>VDRI30B15</t>
+  </si>
+  <si>
+    <t>VDRI30</t>
+  </si>
+  <si>
+    <t>Voltbriks</t>
   </si>
 </sst>
 </file>
@@ -1483,7 +1492,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
@@ -1841,6 +1850,29 @@
       </c>
       <c r="G15" t="s">
         <v>156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>232</v>
+      </c>
+      <c r="B16" t="s">
+        <v>233</v>
+      </c>
+      <c r="C16" t="s">
+        <v>232</v>
+      </c>
+      <c r="D16" t="s">
+        <v>232</v>
+      </c>
+      <c r="E16" t="s">
+        <v>232</v>
+      </c>
+      <c r="F16" t="s">
+        <v>233</v>
+      </c>
+      <c r="G16" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193CE901-EAE1-4122-8B24-4FFF06B34291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B008EAFA-6320-4A98-9141-945083AD7E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2670" yWindow="1920" windowWidth="23085" windowHeight="13635" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="238">
   <si>
     <t>Part Number</t>
   </si>
@@ -858,6 +858,15 @@
   </si>
   <si>
     <t>Voltbriks</t>
+  </si>
+  <si>
+    <t>LM2733</t>
+  </si>
+  <si>
+    <t>LM2733 SOT23-5</t>
+  </si>
+  <si>
+    <t>LM2733XMFX/NOPB</t>
   </si>
 </sst>
 </file>
@@ -1492,7 +1501,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
@@ -1873,6 +1882,29 @@
       </c>
       <c r="G16" t="s">
         <v>234</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>237</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
+        <v>236</v>
+      </c>
+      <c r="D17" t="s">
+        <v>235</v>
+      </c>
+      <c r="E17" t="s">
+        <v>235</v>
+      </c>
+      <c r="F17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B008EAFA-6320-4A98-9141-945083AD7E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7D3E74-BA48-4F19-A41D-80121A6845B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="241">
   <si>
     <t>Part Number</t>
   </si>
@@ -867,6 +867,46 @@
   </si>
   <si>
     <t>LM2733XMFX/NOPB</t>
+  </si>
+  <si>
+    <t>UC348x</t>
+  </si>
+  <si>
+    <r>
+      <t>UC3843</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t>AD8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>UC3843</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t>AD8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 8-SOIC</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -930,13 +970,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
@@ -1501,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
@@ -1904,6 +1945,29 @@
         <v>77</v>
       </c>
       <c r="G17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E18" t="s">
+        <v>238</v>
+      </c>
+      <c r="F18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" t="s">
         <v>8</v>
       </c>
     </row>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7D3E74-BA48-4F19-A41D-80121A6845B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB42A13D-5878-4218-AA82-B873CCA68BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="245">
   <si>
     <t>Part Number</t>
   </si>
@@ -907,6 +907,18 @@
       </rPr>
       <t xml:space="preserve"> 8-SOIC</t>
     </r>
+  </si>
+  <si>
+    <t>LT3757</t>
+  </si>
+  <si>
+    <t>10-MSOP</t>
+  </si>
+  <si>
+    <t>LT3757EMSE</t>
+  </si>
+  <si>
+    <t>LT3757EMSE 10-MSOP</t>
   </si>
 </sst>
 </file>
@@ -970,14 +982,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
@@ -1542,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
@@ -1554,7 +1565,7 @@
     <col min="7" max="7" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1580,7 +1591,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>145</v>
       </c>
@@ -1603,7 +1614,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
         <v>148</v>
       </c>
@@ -1626,7 +1637,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
         <v>152</v>
       </c>
@@ -1649,7 +1660,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
         <v>157</v>
       </c>
@@ -1671,38 +1682,42 @@
       <c r="G5" s="2" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>161</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>165</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -1711,110 +1726,120 @@
       <c r="E7" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="2" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>171</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="G9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
+      <c r="G10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="G11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>187</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1823,153 +1848,291 @@
       <c r="D12" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="G12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="2" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
+      <c r="G14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="2" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="2" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="4" t="s">
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G18" t="s">
-        <v>8</v>
-      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB42A13D-5878-4218-AA82-B873CCA68BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771EEA85-7313-4C50-AFF5-4F7CE3775640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="246">
   <si>
     <t>Part Number</t>
   </si>
@@ -919,6 +919,9 @@
   </si>
   <si>
     <t>LT3757EMSE 10-MSOP</t>
+  </si>
+  <si>
+    <t>10-MSOP (PAD)</t>
   </si>
 </sst>
 </file>
@@ -2027,7 +2030,7 @@
         <v>241</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>156</v>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garou/Documents/work/elem_altium_db2/library/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771EEA85-7313-4C50-AFF5-4F7CE3775640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481AC67C-F78E-8340-AECC-8188B8F9FAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="8" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="misc" sheetId="6" r:id="rId6"/>
     <sheet name="power_mux" sheetId="7" r:id="rId7"/>
     <sheet name="power_switch" sheetId="8" r:id="rId8"/>
-    <sheet name="Vref_sourse" sheetId="9" r:id="rId9"/>
+    <sheet name="Vref_source" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="249">
   <si>
     <t>Part Number</t>
   </si>
@@ -125,9 +125,6 @@
     <t>36-QFN (5x6)</t>
   </si>
   <si>
-    <t>BQ25756E 36-QFN (5x6)</t>
-  </si>
-  <si>
     <t>BQ27441DRZR-G1A</t>
   </si>
   <si>
@@ -356,12 +353,6 @@
     <t>MAX6495ATT+T</t>
   </si>
   <si>
-    <t>6-TDFN</t>
-  </si>
-  <si>
-    <t>MAX6495ATT+T 6-TDFN</t>
-  </si>
-  <si>
     <t>MAX6495</t>
   </si>
   <si>
@@ -491,12 +482,6 @@
     <t>MAX1674EUA</t>
   </si>
   <si>
-    <t>8-MSOP (8uMAX)</t>
-  </si>
-  <si>
-    <t>MAX1674EUA 8uMAX</t>
-  </si>
-  <si>
     <t>8-MSOP</t>
   </si>
   <si>
@@ -563,16 +548,10 @@
     <t>8-SOIC (PAD)</t>
   </si>
   <si>
-    <t>TPS54335ADDAR 8-SOIC</t>
-  </si>
-  <si>
     <t>TPS5433xA</t>
   </si>
   <si>
     <t>TPS54360DDAR</t>
-  </si>
-  <si>
-    <t>TPS54360DDAR 8-SOIC</t>
   </si>
   <si>
     <t>TPS54360</t>
@@ -603,23 +582,7 @@
     <t>LMC7660</t>
   </si>
   <si>
-    <r>
-      <t>LMC7660</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Inter"/>
-      </rPr>
-      <t>IM 8-SOIC</t>
-    </r>
-  </si>
-  <si>
     <t>LMC7660IM</t>
-  </si>
-  <si>
-    <t>LP2951ACDG 8-SOIC</t>
   </si>
   <si>
     <t>LM2776</t>
@@ -695,30 +658,6 @@
         <rFont val="Inter"/>
       </rPr>
       <t>HS6</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>LT8330</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Inter"/>
-      </rPr>
-      <t>HS6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> SOT23-6</t>
     </r>
   </si>
   <si>
@@ -764,6 +703,125 @@
   </si>
   <si>
     <t>14-TSOP-EP</t>
+  </si>
+  <si>
+    <r>
+      <t>LT8330</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HS6</t>
+    </r>
+  </si>
+  <si>
+    <t>142ЕН12</t>
+  </si>
+  <si>
+    <t>бКО.347.098-11 ТУ</t>
+  </si>
+  <si>
+    <t>TO-263-3</t>
+  </si>
+  <si>
+    <t>LM1117SX-5.0</t>
+  </si>
+  <si>
+    <t>LM1117SX-5.0 TO-263-3</t>
+  </si>
+  <si>
+    <t>HRP5</t>
+  </si>
+  <si>
+    <t>BD00FDAWHFP</t>
+  </si>
+  <si>
+    <t>BD00FDAWHFP HRP5</t>
+  </si>
+  <si>
+    <t>ROHM</t>
+  </si>
+  <si>
+    <t>LT3093EMSE</t>
+  </si>
+  <si>
+    <t>12-MSOP (PAD)</t>
+  </si>
+  <si>
+    <t>LT3093</t>
+  </si>
+  <si>
+    <t>VDRI30B15</t>
+  </si>
+  <si>
+    <t>VDRI30</t>
+  </si>
+  <si>
+    <t>Voltbriks</t>
+  </si>
+  <si>
+    <t>LM2733</t>
+  </si>
+  <si>
+    <t>LM2733 SOT23-5</t>
+  </si>
+  <si>
+    <t>LM2733XMFX/NOPB</t>
+  </si>
+  <si>
+    <t>UC348x</t>
+  </si>
+  <si>
+    <r>
+      <t>UC3843</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t>AD8</t>
+    </r>
+  </si>
+  <si>
+    <t>LT3757</t>
+  </si>
+  <si>
+    <t>LT3757EMSE</t>
+  </si>
+  <si>
+    <t>10-MSOP (PAD)</t>
+  </si>
+  <si>
+    <t>QFN-36</t>
+  </si>
+  <si>
+    <t>BQ25756E QFN-36</t>
+  </si>
+  <si>
+    <t>MSOP-8</t>
+  </si>
+  <si>
+    <t>MAX1674EUA MSOP-8</t>
+  </si>
+  <si>
+    <t>SOIC-8</t>
+  </si>
+  <si>
+    <t>TPS54335ADDAR SOIC-8</t>
+  </si>
+  <si>
+    <t>TPS54360DDAR SOIC-8</t>
+  </si>
+  <si>
+    <t>LMC7660IM SOIC-8</t>
   </si>
   <si>
     <r>
@@ -789,7 +847,7 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 14-TSOP-EP</t>
+      <t xml:space="preserve"> TSOP-14</t>
     </r>
   </si>
   <si>
@@ -807,81 +865,16 @@
       </rPr>
       <t>HS6</t>
     </r>
-  </si>
-  <si>
-    <t>142ЕН12</t>
-  </si>
-  <si>
-    <t>бКО.347.098-11 ТУ</t>
-  </si>
-  <si>
-    <t>TO-263-3</t>
-  </si>
-  <si>
-    <t>LM1117SX-5.0</t>
-  </si>
-  <si>
-    <t>LM1117SX-5.0 TO-263-3</t>
-  </si>
-  <si>
-    <t>HRP5</t>
-  </si>
-  <si>
-    <t>BD00FDAWHFP</t>
-  </si>
-  <si>
-    <t>BD00FDAWHFP HRP5</t>
-  </si>
-  <si>
-    <t>ROHM</t>
-  </si>
-  <si>
-    <t>LT3093EMSE</t>
-  </si>
-  <si>
-    <t>12-MSOP (PAD)</t>
-  </si>
-  <si>
-    <t>12-MSOP</t>
-  </si>
-  <si>
-    <t>LT3093EMSE 12-MSOP</t>
-  </si>
-  <si>
-    <t>LT3093</t>
-  </si>
-  <si>
-    <t>VDRI30B15</t>
-  </si>
-  <si>
-    <t>VDRI30</t>
-  </si>
-  <si>
-    <t>Voltbriks</t>
-  </si>
-  <si>
-    <t>LM2733</t>
-  </si>
-  <si>
-    <t>LM2733 SOT23-5</t>
-  </si>
-  <si>
-    <t>LM2733XMFX/NOPB</t>
-  </si>
-  <si>
-    <t>UC348x</t>
-  </si>
-  <si>
-    <r>
-      <t>UC3843</t>
-    </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Inter"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>AD8</t>
+      <t xml:space="preserve"> SOT23-6</t>
     </r>
   </si>
   <si>
@@ -905,23 +898,32 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 8-SOIC</t>
+      <t xml:space="preserve"> SOIC-8</t>
     </r>
   </si>
   <si>
-    <t>LT3757</t>
-  </si>
-  <si>
-    <t>10-MSOP</t>
-  </si>
-  <si>
-    <t>LT3757EMSE</t>
-  </si>
-  <si>
-    <t>LT3757EMSE 10-MSOP</t>
-  </si>
-  <si>
-    <t>10-MSOP (PAD)</t>
+    <t>LT3757EMSE MSOP-10</t>
+  </si>
+  <si>
+    <t>MSOP-10</t>
+  </si>
+  <si>
+    <t>LP2951ACDG SOIC-8</t>
+  </si>
+  <si>
+    <t>MIC29502 TO-263-6</t>
+  </si>
+  <si>
+    <t>MSOP-12</t>
+  </si>
+  <si>
+    <t>LT3093EMSE MSOP-12</t>
+  </si>
+  <si>
+    <t>TDFN-6</t>
+  </si>
+  <si>
+    <t>MAX6495ATT+T TDFN-6</t>
   </si>
 </sst>
 </file>
@@ -994,8 +996,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1011,9 +1013,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1051,7 +1053,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1157,7 +1159,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1299,7 +1301,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1308,15 +1310,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1370,22 +1368,22 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
@@ -1399,13 +1397,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.140625" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" customWidth="1"/>
-    <col min="7" max="7" width="21.5703125" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1480,15 +1476,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" ht="16">
       <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>230</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>231</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
@@ -1505,22 +1501,22 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
         <v>28</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>31</v>
-      </c>
-      <c r="F5" t="s">
-        <v>32</v>
       </c>
       <c r="G5" t="s">
         <v>8</v>
@@ -1528,22 +1524,22 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
         <v>34</v>
       </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>35</v>
-      </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
         <v>8</v>
@@ -1557,15 +1553,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
   <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="3" max="3" width="27.140625" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
-    <col min="7" max="7" width="20.5703125" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1596,22 +1588,22 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -1619,143 +1611,143 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>232</v>
       </c>
       <c r="C3" t="s">
-        <v>150</v>
+        <v>233</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>11</v>
@@ -1765,22 +1757,22 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>173</v>
+        <v>235</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>8</v>
@@ -1790,22 +1782,22 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>8</v>
@@ -1815,19 +1807,19 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>9</v>
+        <v>234</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>183</v>
+        <v>237</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>9</v>
@@ -1840,22 +1832,22 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>8</v>
@@ -1865,47 +1857,47 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>8</v>
@@ -1915,72 +1907,72 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>8</v>
@@ -1990,19 +1982,19 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>9</v>
+        <v>234</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>240</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>9</v>
@@ -2015,25 +2007,25 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>242</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -2145,13 +2137,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD41208-6905-41A5-8CDA-45891F714057}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2182,45 +2172,45 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3" t="s">
         <v>138</v>
-      </c>
-      <c r="B3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F3" t="s">
-        <v>141</v>
       </c>
       <c r="G3" t="s">
         <v>8</v>
@@ -2228,22 +2218,22 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s">
         <v>8</v>
@@ -2257,14 +2247,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
   <dimension ref="A1:H38"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2295,22 +2282,22 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
         <v>37</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>37</v>
-      </c>
-      <c r="E2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" t="s">
-        <v>38</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -2318,22 +2305,22 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>42</v>
-      </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s">
         <v>8</v>
@@ -2341,22 +2328,22 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
         <v>43</v>
       </c>
-      <c r="B4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" t="s">
-        <v>44</v>
-      </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s">
         <v>8</v>
@@ -2364,22 +2351,22 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
         <v>45</v>
       </c>
-      <c r="B5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" t="s">
-        <v>46</v>
-      </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
         <v>8</v>
@@ -2387,22 +2374,22 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
         <v>47</v>
       </c>
-      <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" t="s">
-        <v>48</v>
-      </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
         <v>8</v>
@@ -2410,22 +2397,22 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
         <v>49</v>
       </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>50</v>
-      </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G7" t="s">
         <v>8</v>
@@ -2433,22 +2420,22 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
         <v>51</v>
       </c>
-      <c r="B8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" t="s">
-        <v>52</v>
-      </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
         <v>8</v>
@@ -2456,22 +2443,22 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
         <v>53</v>
       </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" t="s">
-        <v>54</v>
-      </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G9" t="s">
         <v>8</v>
@@ -2479,22 +2466,22 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
         <v>55</v>
       </c>
-      <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" t="s">
-        <v>56</v>
-      </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G10" t="s">
         <v>8</v>
@@ -2502,22 +2489,22 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
         <v>57</v>
       </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>58</v>
-      </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G11" t="s">
         <v>8</v>
@@ -2525,22 +2512,22 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
         <v>59</v>
       </c>
-      <c r="B12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" t="s">
         <v>60</v>
       </c>
-      <c r="D12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" t="s">
-        <v>61</v>
-      </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G12" t="s">
         <v>8</v>
@@ -2548,22 +2535,22 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
         <v>62</v>
       </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" t="s">
-        <v>63</v>
-      </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G13" t="s">
         <v>8</v>
@@ -2571,22 +2558,22 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
         <v>64</v>
       </c>
-      <c r="B14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" t="s">
-        <v>65</v>
-      </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G14" t="s">
         <v>8</v>
@@ -2594,22 +2581,22 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
         <v>66</v>
       </c>
-      <c r="B15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" t="s">
-        <v>67</v>
-      </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G15" t="s">
         <v>8</v>
@@ -2617,22 +2604,22 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
         <v>68</v>
       </c>
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" t="s">
-        <v>69</v>
-      </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G16" t="s">
         <v>8</v>
@@ -2640,22 +2627,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
         <v>70</v>
       </c>
-      <c r="B17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" t="s">
-        <v>71</v>
-      </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G17" t="s">
         <v>8</v>
@@ -2663,22 +2650,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
         <v>72</v>
       </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>73</v>
-      </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G18" t="s">
         <v>8</v>
@@ -2686,22 +2673,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
         <v>74</v>
       </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>75</v>
-      </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G19" t="s">
         <v>8</v>
@@ -2709,22 +2696,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" t="s">
         <v>76</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>77</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" t="s">
         <v>78</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
         <v>76</v>
-      </c>
-      <c r="E20" t="s">
-        <v>79</v>
-      </c>
-      <c r="F20" t="s">
-        <v>77</v>
       </c>
       <c r="G20" t="s">
         <v>8</v>
@@ -2732,22 +2719,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" t="s">
         <v>80</v>
       </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" t="s">
-        <v>81</v>
-      </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s">
         <v>8</v>
@@ -2755,22 +2742,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
         <v>82</v>
       </c>
-      <c r="B22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" t="s">
-        <v>83</v>
-      </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s">
         <v>8</v>
@@ -2778,22 +2765,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" t="s">
         <v>84</v>
       </c>
-      <c r="B23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" t="s">
-        <v>85</v>
-      </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G23" t="s">
         <v>8</v>
@@ -2801,22 +2788,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" t="s">
         <v>86</v>
       </c>
-      <c r="B24" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" t="s">
-        <v>87</v>
-      </c>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G24" t="s">
         <v>8</v>
@@ -2824,137 +2811,137 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" t="s">
         <v>88</v>
       </c>
-      <c r="B25" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" t="s">
         <v>89</v>
       </c>
-      <c r="D25" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" t="s">
         <v>90</v>
-      </c>
-      <c r="F25" t="s">
-        <v>77</v>
-      </c>
-      <c r="G25" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" t="s">
         <v>92</v>
       </c>
-      <c r="B26" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" t="s">
-        <v>93</v>
-      </c>
       <c r="D26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E26" t="s">
+        <v>89</v>
+      </c>
+      <c r="F26" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" t="s">
         <v>90</v>
-      </c>
-      <c r="F26" t="s">
-        <v>77</v>
-      </c>
-      <c r="G26" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" t="s">
         <v>94</v>
       </c>
-      <c r="B27" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" t="s">
-        <v>95</v>
-      </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" t="s">
         <v>90</v>
-      </c>
-      <c r="F27" t="s">
-        <v>77</v>
-      </c>
-      <c r="G27" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" t="s">
         <v>96</v>
       </c>
-      <c r="B28" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" t="s">
-        <v>97</v>
-      </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E28" t="s">
+        <v>89</v>
+      </c>
+      <c r="F28" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" t="s">
         <v>90</v>
-      </c>
-      <c r="F28" t="s">
-        <v>77</v>
-      </c>
-      <c r="G28" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" t="s">
         <v>98</v>
       </c>
-      <c r="B29" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" t="s">
-        <v>99</v>
-      </c>
       <c r="D29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E29" t="s">
+        <v>89</v>
+      </c>
+      <c r="F29" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" t="s">
         <v>90</v>
-      </c>
-      <c r="F29" t="s">
-        <v>77</v>
-      </c>
-      <c r="G29" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G30" t="s">
         <v>11</v>
@@ -2962,137 +2949,134 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>234</v>
       </c>
       <c r="C31" t="s">
-        <v>185</v>
+        <v>243</v>
       </c>
       <c r="D31" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="E31" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B32" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C32" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D32" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E32" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F32" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="G32" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="B33" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C33" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D33" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="E33" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="F33" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G33" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B34" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C34" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="D34" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="E34" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F34" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="G34" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>218</v>
-      </c>
-      <c r="B35" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="C35" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="D35" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E35" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F35" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="H35" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="B36" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C36" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="D36" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F36" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="G36" t="s">
         <v>8</v>
@@ -3100,48 +3084,48 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B37" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="C37" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="D37" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="E37" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="F37" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="G37" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="B38" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="C38" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="D38" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E38" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="F38" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3152,14 +3136,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79FF623C-E451-4C0A-BB30-6BFAFBFB995B}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3190,45 +3171,45 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" t="s">
         <v>101</v>
-      </c>
-      <c r="C2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" t="s">
         <v>103</v>
       </c>
-      <c r="B3" t="s">
+      <c r="F3" t="s">
         <v>104</v>
       </c>
-      <c r="C3" t="s">
+      <c r="G3" t="s">
         <v>105</v>
-      </c>
-      <c r="D3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G3" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -3239,11 +3220,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{502B3B07-F695-4F0E-B776-807579F5C093}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3274,45 +3255,45 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H2" t="s">
         <v>109</v>
-      </c>
-      <c r="B2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" t="s">
         <v>113</v>
       </c>
-      <c r="B3" t="s">
+      <c r="F3" t="s">
         <v>114</v>
-      </c>
-      <c r="C3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F3" t="s">
-        <v>117</v>
       </c>
       <c r="G3" t="s">
         <v>8</v>
@@ -3320,22 +3301,22 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" t="s">
         <v>114</v>
-      </c>
-      <c r="C4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F4" t="s">
-        <v>117</v>
       </c>
       <c r="G4" t="s">
         <v>8</v>
@@ -3343,22 +3324,22 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" t="s">
         <v>120</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F5" t="s">
         <v>121</v>
-      </c>
-      <c r="C5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" t="s">
-        <v>123</v>
-      </c>
-      <c r="F5" t="s">
-        <v>124</v>
       </c>
       <c r="G5" t="s">
         <v>8</v>
@@ -3372,13 +3353,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE80AA7D-5B01-4429-B668-37BD5F31C3F5}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3409,70 +3388,70 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
         <v>8</v>
@@ -3487,14 +3466,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F703D42-6E7A-4C3C-A172-8A9EBFFB14A6}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.140625" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3525,25 +3501,25 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="B2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" t="s">
         <v>190</v>
       </c>
-      <c r="C2" t="s">
-        <v>199</v>
-      </c>
       <c r="D2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="F2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garou/Documents/work/elem_altium_db2/library/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481AC67C-F78E-8340-AECC-8188B8F9FAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BFAAA12-57E9-4FA3-8B22-7D8EB6A22E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="8" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="253">
   <si>
     <t>Part Number</t>
   </si>
@@ -924,6 +924,18 @@
   </si>
   <si>
     <t>MAX6495ATT+T TDFN-6</t>
+  </si>
+  <si>
+    <t>LM27762DSS</t>
+  </si>
+  <si>
+    <t>12-WSON</t>
+  </si>
+  <si>
+    <t>LM27762</t>
+  </si>
+  <si>
+    <t>LM27762DSS 12-WSON</t>
   </si>
 </sst>
 </file>
@@ -996,8 +1008,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1013,9 +1025,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1053,7 +1065,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1159,7 +1171,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1301,7 +1313,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1310,11 +1322,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1397,11 +1409,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1476,7 +1488,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="16">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1552,12 +1564,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
-  <dimension ref="A1:I28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2031,13 +2043,27 @@
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
@@ -2129,6 +2155,16 @@
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
     </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2137,11 +2173,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD41208-6905-41A5-8CDA-45891F714057}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2247,11 +2283,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
   <dimension ref="A1:H38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3136,11 +3172,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79FF623C-E451-4C0A-BB30-6BFAFBFB995B}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3220,11 +3256,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{502B3B07-F695-4F0E-B776-807579F5C093}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3353,11 +3389,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE80AA7D-5B01-4429-B668-37BD5F31C3F5}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3466,11 +3502,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F703D42-6E7A-4C3C-A172-8A9EBFFB14A6}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BFAAA12-57E9-4FA3-8B22-7D8EB6A22E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF33AFFB-55D8-4985-B83D-0AB00FE7F389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="255">
   <si>
     <t>Part Number</t>
   </si>
@@ -936,6 +936,12 @@
   </si>
   <si>
     <t>LM27762DSS 12-WSON</t>
+  </si>
+  <si>
+    <t>LM217MDT</t>
+  </si>
+  <si>
+    <t>LM217MDT SOT223</t>
   </si>
 </sst>
 </file>
@@ -2282,7 +2288,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.85546875" customWidth="1"/>
@@ -3160,8 +3166,31 @@
       <c r="F38" t="s">
         <v>217</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" t="s">
         <v>151</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>253</v>
+      </c>
+      <c r="B39" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" t="s">
+        <v>254</v>
+      </c>
+      <c r="D39" t="s">
+        <v>253</v>
+      </c>
+      <c r="E39" t="s">
+        <v>60</v>
+      </c>
+      <c r="F39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G39" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF33AFFB-55D8-4985-B83D-0AB00FE7F389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B46DEC-958C-4462-B577-31ACEA45F492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -938,10 +938,10 @@
     <t>LM27762DSS 12-WSON</t>
   </si>
   <si>
-    <t>LM217MDT</t>
-  </si>
-  <si>
-    <t>LM217MDT SOT223</t>
+    <t>LM217T</t>
+  </si>
+  <si>
+    <t>LM217T SOT223</t>
   </si>
 </sst>
 </file>
@@ -3184,17 +3184,18 @@
         <v>253</v>
       </c>
       <c r="E39" t="s">
-        <v>60</v>
+        <v>253</v>
       </c>
       <c r="F39" t="s">
         <v>37</v>
       </c>
       <c r="G39" t="s">
-        <v>8</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B46DEC-958C-4462-B577-31ACEA45F492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6528E6BE-EEB2-4AE6-A754-46588C843937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -751,9 +751,6 @@
     <t>LT3093EMSE</t>
   </si>
   <si>
-    <t>12-MSOP (PAD)</t>
-  </si>
-  <si>
     <t>LT3093</t>
   </si>
   <si>
@@ -942,6 +939,9 @@
   </si>
   <si>
     <t>LM217T SOT223</t>
+  </si>
+  <si>
+    <t>12-MSOP W (PAD)</t>
   </si>
 </sst>
 </file>
@@ -1499,10 +1499,10 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4" t="s">
         <v>230</v>
-      </c>
-      <c r="C4" t="s">
-        <v>231</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
@@ -1632,10 +1632,10 @@
         <v>145</v>
       </c>
       <c r="B3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" t="s">
         <v>232</v>
-      </c>
-      <c r="C3" t="s">
-        <v>233</v>
       </c>
       <c r="D3" t="s">
         <v>145</v>
@@ -1778,10 +1778,10 @@
         <v>166</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>166</v>
@@ -1803,10 +1803,10 @@
         <v>169</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>169</v>
@@ -1828,10 +1828,10 @@
         <v>176</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>176</v>
@@ -1906,7 +1906,7 @@
         <v>205</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>204</v>
@@ -1931,7 +1931,7 @@
         <v>35</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>206</v>
@@ -1950,44 +1950,44 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>76</v>
@@ -2000,19 +2000,19 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>9</v>
@@ -2025,22 +2025,22 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>229</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>151</v>
@@ -2050,22 +2050,22 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>250</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>8</v>
@@ -2994,10 +2994,10 @@
         <v>172</v>
       </c>
       <c r="B31" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C31" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D31" t="s">
         <v>172</v>
@@ -3066,7 +3066,7 @@
         <v>200</v>
       </c>
       <c r="C34" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D34" t="s">
         <v>199</v>
@@ -3152,19 +3152,19 @@
         <v>216</v>
       </c>
       <c r="B38" t="s">
+        <v>244</v>
+      </c>
+      <c r="C38" t="s">
         <v>245</v>
-      </c>
-      <c r="C38" t="s">
-        <v>246</v>
       </c>
       <c r="D38" t="s">
         <v>216</v>
       </c>
       <c r="E38" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F38" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="G38" t="s">
         <v>151</v>
@@ -3172,19 +3172,19 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
+        <v>252</v>
+      </c>
+      <c r="B39" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" t="s">
         <v>253</v>
       </c>
-      <c r="B39" t="s">
-        <v>37</v>
-      </c>
-      <c r="C39" t="s">
-        <v>254</v>
-      </c>
       <c r="D39" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E39" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F39" t="s">
         <v>37</v>
@@ -3260,10 +3260,10 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C3" t="s">
         <v>247</v>
-      </c>
-      <c r="C3" t="s">
-        <v>248</v>
       </c>
       <c r="D3" t="s">
         <v>102</v>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6528E6BE-EEB2-4AE6-A754-46588C843937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A5E980-2FA9-4295-8932-CB5A24B93932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="260">
   <si>
     <t>Part Number</t>
   </si>
@@ -646,19 +646,6 @@
   </si>
   <si>
     <t>LT8330</t>
-  </si>
-  <si>
-    <r>
-      <t>LT8330</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Inter"/>
-      </rPr>
-      <t>HS6</t>
-    </r>
   </si>
   <si>
     <t>MIC29502</t>
@@ -775,50 +762,137 @@
     <t>UC348x</t>
   </si>
   <si>
+    <t>LT3757</t>
+  </si>
+  <si>
+    <t>LT3757EMSE</t>
+  </si>
+  <si>
+    <t>10-MSOP (PAD)</t>
+  </si>
+  <si>
+    <t>QFN-36</t>
+  </si>
+  <si>
+    <t>BQ25756E QFN-36</t>
+  </si>
+  <si>
+    <t>MSOP-8</t>
+  </si>
+  <si>
+    <t>MAX1674EUA MSOP-8</t>
+  </si>
+  <si>
+    <t>SOIC-8</t>
+  </si>
+  <si>
+    <t>TPS54335ADDAR SOIC-8</t>
+  </si>
+  <si>
+    <t>TPS54360DDAR SOIC-8</t>
+  </si>
+  <si>
+    <t>LMC7660IM SOIC-8</t>
+  </si>
+  <si>
+    <t>LT3757EMSE MSOP-10</t>
+  </si>
+  <si>
+    <t>MSOP-10</t>
+  </si>
+  <si>
+    <t>LP2951ACDG SOIC-8</t>
+  </si>
+  <si>
+    <t>MIC29502 TO-263-6</t>
+  </si>
+  <si>
+    <t>MSOP-12</t>
+  </si>
+  <si>
+    <t>LT3093EMSE MSOP-12</t>
+  </si>
+  <si>
+    <t>TDFN-6</t>
+  </si>
+  <si>
+    <t>MAX6495ATT+T TDFN-6</t>
+  </si>
+  <si>
+    <t>LM27762DSS</t>
+  </si>
+  <si>
+    <t>12-WSON</t>
+  </si>
+  <si>
+    <t>LM27762</t>
+  </si>
+  <si>
+    <t>LM27762DSS 12-WSON</t>
+  </si>
+  <si>
+    <t>LM217T</t>
+  </si>
+  <si>
+    <t>LM217T SOT223</t>
+  </si>
+  <si>
+    <t>12-MSOP W (PAD)</t>
+  </si>
+  <si>
+    <t>LM217MDT</t>
+  </si>
+  <si>
+    <t>TO-252-2</t>
+  </si>
+  <si>
+    <t>LM217MDT TO-252-2</t>
+  </si>
+  <si>
+    <t>UCx825</t>
+  </si>
+  <si>
     <r>
-      <t>UC3843</t>
+      <t>UC3825</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="Inter"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>AD8</t>
+      <t>BDW</t>
     </r>
   </si>
   <si>
-    <t>LT3757</t>
-  </si>
-  <si>
-    <t>LT3757EMSE</t>
-  </si>
-  <si>
-    <t>10-MSOP (PAD)</t>
-  </si>
-  <si>
-    <t>QFN-36</t>
-  </si>
-  <si>
-    <t>BQ25756E QFN-36</t>
-  </si>
-  <si>
-    <t>MSOP-8</t>
-  </si>
-  <si>
-    <t>MAX1674EUA MSOP-8</t>
-  </si>
-  <si>
-    <t>SOIC-8</t>
-  </si>
-  <si>
-    <t>TPS54335ADDAR SOIC-8</t>
-  </si>
-  <si>
-    <t>TPS54360DDAR SOIC-8</t>
-  </si>
-  <si>
-    <t>LMC7660IM SOIC-8</t>
+    <r>
+      <t>UC3825</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BDW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 16-SOIC</t>
+    </r>
   </si>
   <si>
     <r>
@@ -880,9 +954,28 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="Inter"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AD8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>UC3843</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
       </rPr>
       <t>AD8</t>
     </r>
@@ -898,57 +991,12 @@
       <t xml:space="preserve"> SOIC-8</t>
     </r>
   </si>
-  <si>
-    <t>LT3757EMSE MSOP-10</t>
-  </si>
-  <si>
-    <t>MSOP-10</t>
-  </si>
-  <si>
-    <t>LP2951ACDG SOIC-8</t>
-  </si>
-  <si>
-    <t>MIC29502 TO-263-6</t>
-  </si>
-  <si>
-    <t>MSOP-12</t>
-  </si>
-  <si>
-    <t>LT3093EMSE MSOP-12</t>
-  </si>
-  <si>
-    <t>TDFN-6</t>
-  </si>
-  <si>
-    <t>MAX6495ATT+T TDFN-6</t>
-  </si>
-  <si>
-    <t>LM27762DSS</t>
-  </si>
-  <si>
-    <t>12-WSON</t>
-  </si>
-  <si>
-    <t>LM27762</t>
-  </si>
-  <si>
-    <t>LM27762DSS 12-WSON</t>
-  </si>
-  <si>
-    <t>LM217T</t>
-  </si>
-  <si>
-    <t>LM217T SOT223</t>
-  </si>
-  <si>
-    <t>12-MSOP W (PAD)</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -972,6 +1020,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -1005,13 +1061,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
@@ -1499,10 +1557,10 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
@@ -1605,493 +1663,507 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" t="s">
+      <c r="A2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C3" t="s">
-        <v>232</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B3" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="4" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="4" t="s">
         <v>151</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="4" t="s">
         <v>105</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="4" t="s">
         <v>161</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="B9" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="B11" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="C14" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="C15" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="4" t="s">
         <v>151</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>219</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>220</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="A17" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="C17" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="D17" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="A18" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="A19" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="4" t="s">
         <v>151</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G20" s="2" t="s">
+      <c r="A20" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
+      <c r="A21" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
     </row>
@@ -2288,7 +2360,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.85546875" customWidth="1"/>
@@ -2994,10 +3066,10 @@
         <v>172</v>
       </c>
       <c r="B31" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C31" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D31" t="s">
         <v>172</v>
@@ -3060,65 +3132,65 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B34" t="s">
+        <v>199</v>
+      </c>
+      <c r="C34" t="s">
+        <v>238</v>
+      </c>
+      <c r="D34" t="s">
+        <v>198</v>
+      </c>
+      <c r="E34" t="s">
+        <v>198</v>
+      </c>
+      <c r="F34" t="s">
+        <v>199</v>
+      </c>
+      <c r="G34" t="s">
         <v>200</v>
-      </c>
-      <c r="C34" t="s">
-        <v>243</v>
-      </c>
-      <c r="D34" t="s">
-        <v>199</v>
-      </c>
-      <c r="E34" t="s">
-        <v>199</v>
-      </c>
-      <c r="F34" t="s">
-        <v>200</v>
-      </c>
-      <c r="G34" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
+        <v>206</v>
+      </c>
+      <c r="C35" t="s">
+        <v>206</v>
+      </c>
+      <c r="D35" t="s">
+        <v>206</v>
+      </c>
+      <c r="E35" t="s">
+        <v>206</v>
+      </c>
+      <c r="F35" t="s">
+        <v>206</v>
+      </c>
+      <c r="H35" t="s">
         <v>207</v>
-      </c>
-      <c r="C35" t="s">
-        <v>207</v>
-      </c>
-      <c r="D35" t="s">
-        <v>207</v>
-      </c>
-      <c r="E35" t="s">
-        <v>207</v>
-      </c>
-      <c r="F35" t="s">
-        <v>207</v>
-      </c>
-      <c r="H35" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
+        <v>209</v>
+      </c>
+      <c r="B36" t="s">
+        <v>208</v>
+      </c>
+      <c r="C36" t="s">
         <v>210</v>
       </c>
-      <c r="B36" t="s">
+      <c r="D36" t="s">
         <v>209</v>
-      </c>
-      <c r="C36" t="s">
-        <v>211</v>
-      </c>
-      <c r="D36" t="s">
-        <v>210</v>
       </c>
       <c r="E36" t="s">
         <v>39</v>
       </c>
       <c r="F36" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G36" t="s">
         <v>8</v>
@@ -3126,45 +3198,45 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
+        <v>212</v>
+      </c>
+      <c r="B37" t="s">
+        <v>211</v>
+      </c>
+      <c r="C37" t="s">
         <v>213</v>
       </c>
-      <c r="B37" t="s">
+      <c r="D37" t="s">
         <v>212</v>
       </c>
-      <c r="C37" t="s">
+      <c r="E37" t="s">
+        <v>212</v>
+      </c>
+      <c r="F37" t="s">
+        <v>211</v>
+      </c>
+      <c r="G37" t="s">
         <v>214</v>
-      </c>
-      <c r="D37" t="s">
-        <v>213</v>
-      </c>
-      <c r="E37" t="s">
-        <v>213</v>
-      </c>
-      <c r="F37" t="s">
-        <v>212</v>
-      </c>
-      <c r="G37" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
+        <v>215</v>
+      </c>
+      <c r="B38" t="s">
+        <v>239</v>
+      </c>
+      <c r="C38" t="s">
+        <v>240</v>
+      </c>
+      <c r="D38" t="s">
+        <v>215</v>
+      </c>
+      <c r="E38" t="s">
         <v>216</v>
       </c>
-      <c r="B38" t="s">
-        <v>244</v>
-      </c>
-      <c r="C38" t="s">
-        <v>245</v>
-      </c>
-      <c r="D38" t="s">
-        <v>216</v>
-      </c>
-      <c r="E38" t="s">
-        <v>217</v>
-      </c>
       <c r="F38" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="G38" t="s">
         <v>151</v>
@@ -3172,24 +3244,47 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
+        <v>247</v>
+      </c>
+      <c r="B39" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" t="s">
+        <v>248</v>
+      </c>
+      <c r="D39" t="s">
+        <v>247</v>
+      </c>
+      <c r="E39" t="s">
+        <v>247</v>
+      </c>
+      <c r="F39" t="s">
+        <v>37</v>
+      </c>
+      <c r="G39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>250</v>
+      </c>
+      <c r="B40" t="s">
+        <v>251</v>
+      </c>
+      <c r="C40" t="s">
         <v>252</v>
       </c>
-      <c r="B39" t="s">
-        <v>37</v>
-      </c>
-      <c r="C39" t="s">
-        <v>253</v>
-      </c>
-      <c r="D39" t="s">
-        <v>252</v>
-      </c>
-      <c r="E39" t="s">
-        <v>252</v>
-      </c>
-      <c r="F39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G39" t="s">
+      <c r="D40" t="s">
+        <v>250</v>
+      </c>
+      <c r="E40" t="s">
+        <v>247</v>
+      </c>
+      <c r="F40" t="s">
+        <v>251</v>
+      </c>
+      <c r="G40" t="s">
         <v>196</v>
       </c>
     </row>
@@ -3260,10 +3355,10 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D3" t="s">
         <v>102</v>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A5E980-2FA9-4295-8932-CB5A24B93932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DAC53A-541F-4D1A-B2DE-7150129A7DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="270">
   <si>
     <t>Part Number</t>
   </si>
@@ -832,9 +832,6 @@
   </si>
   <si>
     <t>LM217T</t>
-  </si>
-  <si>
-    <t>LM217T SOT223</t>
   </si>
   <si>
     <t>12-MSOP W (PAD)</t>
@@ -991,12 +988,45 @@
       <t xml:space="preserve"> SOIC-8</t>
     </r>
   </si>
+  <si>
+    <t>16-SOIC (W)</t>
+  </si>
+  <si>
+    <t>UC2825</t>
+  </si>
+  <si>
+    <t>UC2825DWTR</t>
+  </si>
+  <si>
+    <t>UC2825DWTR 16-SOIC (W)</t>
+  </si>
+  <si>
+    <t>SG2525A</t>
+  </si>
+  <si>
+    <t>SG2525AP013TR</t>
+  </si>
+  <si>
+    <t>SG2525AP013TR 16-SOIC</t>
+  </si>
+  <si>
+    <t>АЕЯР.431420.007-02ТУ</t>
+  </si>
+  <si>
+    <t>1156ЕУ2</t>
+  </si>
+  <si>
+    <t>TO-220</t>
+  </si>
+  <si>
+    <t>LM217T TO-220</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1020,14 +1050,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -1061,15 +1083,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
@@ -1663,530 +1683,568 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" t="s">
         <v>143</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" t="s">
         <v>142</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" t="s">
         <v>144</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" t="s">
         <v>229</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" t="s">
         <v>230</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" t="s">
         <v>145</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" t="s">
         <v>146</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="2" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="2" t="s">
         <v>151</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="2" t="s">
         <v>105</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="2" t="s">
         <v>161</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="2" t="s">
         <v>188</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="C14" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="C15" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="2" t="s">
         <v>151</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="2" t="s">
         <v>219</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="E18" s="4" t="s">
+      <c r="D18" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="2" t="s">
         <v>151</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="D21" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="A22" t="s">
+        <v>261</v>
+      </c>
+      <c r="B22" t="s">
+        <v>259</v>
+      </c>
+      <c r="C22" t="s">
+        <v>262</v>
+      </c>
+      <c r="D22" t="s">
+        <v>261</v>
+      </c>
+      <c r="E22" t="s">
+        <v>260</v>
+      </c>
+      <c r="F22" t="s">
+        <v>259</v>
+      </c>
+      <c r="G22" t="s">
+        <v>8</v>
+      </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
+      <c r="A23" t="s">
+        <v>264</v>
+      </c>
+      <c r="B23" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" t="s">
+        <v>265</v>
+      </c>
+      <c r="D23" t="s">
+        <v>264</v>
+      </c>
+      <c r="E23" t="s">
+        <v>263</v>
+      </c>
+      <c r="F23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G23" t="s">
+        <v>196</v>
+      </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
+      <c r="A24" t="s">
+        <v>267</v>
+      </c>
+      <c r="C24" t="s">
+        <v>267</v>
+      </c>
+      <c r="D24" t="s">
+        <v>267</v>
+      </c>
+      <c r="E24" t="s">
+        <v>267</v>
+      </c>
+      <c r="F24" t="s">
+        <v>267</v>
+      </c>
+      <c r="H24" t="s">
+        <v>266</v>
+      </c>
       <c r="I24" s="2"/>
     </row>
     <row r="25" spans="1:9">
@@ -3236,7 +3294,7 @@
         <v>216</v>
       </c>
       <c r="F38" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G38" t="s">
         <v>151</v>
@@ -3247,10 +3305,10 @@
         <v>247</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>268</v>
       </c>
       <c r="C39" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="D39" t="s">
         <v>247</v>
@@ -3259,7 +3317,7 @@
         <v>247</v>
       </c>
       <c r="F39" t="s">
-        <v>37</v>
+        <v>268</v>
       </c>
       <c r="G39" t="s">
         <v>196</v>
@@ -3267,22 +3325,22 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
+        <v>249</v>
+      </c>
+      <c r="B40" t="s">
         <v>250</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>251</v>
       </c>
-      <c r="C40" t="s">
-        <v>252</v>
-      </c>
       <c r="D40" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E40" t="s">
         <v>247</v>
       </c>
       <c r="F40" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G40" t="s">
         <v>196</v>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DAC53A-541F-4D1A-B2DE-7150129A7DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991EE40C-AF11-4FFE-B2DC-2FA8B2E6231D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="272">
   <si>
     <t>Part Number</t>
   </si>
@@ -1020,6 +1020,12 @@
   </si>
   <si>
     <t>LM217T TO-220</t>
+  </si>
+  <si>
+    <t>URB2405LD-20WR3</t>
+  </si>
+  <si>
+    <t>Mornsun Power</t>
   </si>
 </sst>
 </file>
@@ -1083,13 +1089,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
@@ -2177,84 +2184,100 @@
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" t="s">
+      <c r="A22" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" t="s">
+      <c r="A23" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="2" t="s">
         <v>196</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" t="s">
+      <c r="A24" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C24" t="s">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="H24" t="s">
+      <c r="G24" s="2"/>
+      <c r="H24" s="2" t="s">
         <v>266</v>
       </c>
       <c r="I24" s="2"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+      <c r="A25" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>271</v>
+      </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
     </row>
@@ -2303,6 +2326,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991EE40C-AF11-4FFE-B2DC-2FA8B2E6231D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6293BB0A-9ED1-4BE6-86AC-EA63EBB9BFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="279">
   <si>
     <t>Part Number</t>
   </si>
@@ -1026,6 +1026,27 @@
   </si>
   <si>
     <t>Mornsun Power</t>
+  </si>
+  <si>
+    <t>HY2213</t>
+  </si>
+  <si>
+    <t>HY2213-BB3A</t>
+  </si>
+  <si>
+    <t>HY2213-BB3A SOT23-6</t>
+  </si>
+  <si>
+    <t>HYCON</t>
+  </si>
+  <si>
+    <t>LM317AMDT</t>
+  </si>
+  <si>
+    <t>LDO 3I2O1A</t>
+  </si>
+  <si>
+    <t>LM317AMDT TO-252-2</t>
   </si>
 </sst>
 </file>
@@ -1089,14 +1110,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
@@ -1499,7 +1519,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.85546875" customWidth="1"/>
@@ -1646,6 +1666,29 @@
       </c>
       <c r="G6" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>273</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D7" t="s">
+        <v>273</v>
+      </c>
+      <c r="E7" t="s">
+        <v>272</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -2275,7 +2318,7 @@
       <c r="F25" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" t="s">
         <v>271</v>
       </c>
       <c r="H25" s="2"/>
@@ -2442,7 +2485,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.85546875" customWidth="1"/>
@@ -3338,7 +3381,7 @@
         <v>247</v>
       </c>
       <c r="E39" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="F39" t="s">
         <v>268</v>
@@ -3361,13 +3404,36 @@
         <v>249</v>
       </c>
       <c r="E40" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="F40" t="s">
         <v>250</v>
       </c>
       <c r="G40" t="s">
         <v>196</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>276</v>
+      </c>
+      <c r="B41" t="s">
+        <v>250</v>
+      </c>
+      <c r="C41" t="s">
+        <v>278</v>
+      </c>
+      <c r="D41" t="s">
+        <v>276</v>
+      </c>
+      <c r="E41" t="s">
+        <v>277</v>
+      </c>
+      <c r="F41" t="s">
+        <v>250</v>
+      </c>
+      <c r="G41" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6293BB0A-9ED1-4BE6-86AC-EA63EBB9BFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871AB975-F8F0-4973-A299-E32A1A881C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ac-dc" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="282">
   <si>
     <t>Part Number</t>
   </si>
@@ -1047,6 +1047,15 @@
   </si>
   <si>
     <t>LM317AMDT TO-252-2</t>
+  </si>
+  <si>
+    <t>SOT-23</t>
+  </si>
+  <si>
+    <t>Diode Zener_adj</t>
+  </si>
+  <si>
+    <t>TL431AQDBZR</t>
   </si>
 </sst>
 </file>
@@ -2485,7 +2494,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.85546875" customWidth="1"/>
@@ -3433,6 +3442,30 @@
         <v>250</v>
       </c>
       <c r="G41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>281</v>
+      </c>
+      <c r="B42" t="s">
+        <v>279</v>
+      </c>
+      <c r="C42" t="str">
+        <f>_xlfn.CONCAT(D42, " ", B42)</f>
+        <v>TL431AQDBZR SOT-23</v>
+      </c>
+      <c r="D42" t="s">
+        <v>281</v>
+      </c>
+      <c r="E42" t="s">
+        <v>280</v>
+      </c>
+      <c r="F42" t="s">
+        <v>279</v>
+      </c>
+      <c r="G42" t="s">
         <v>8</v>
       </c>
     </row>

--- a/library/power_supplies.xlsx
+++ b/library/power_supplies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871AB975-F8F0-4973-A299-E32A1A881C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822652DF-7A6E-4F73-A1AE-42582B23F379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="281">
   <si>
     <t>Part Number</t>
   </si>
@@ -1047,9 +1047,6 @@
   </si>
   <si>
     <t>LM317AMDT TO-252-2</t>
-  </si>
-  <si>
-    <t>SOT-23</t>
   </si>
   <si>
     <t>Diode Zener_adj</t>
@@ -3447,23 +3444,23 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B42" t="s">
-        <v>279</v>
+        <v>181</v>
       </c>
       <c r="C42" t="str">
         <f>_xlfn.CONCAT(D42, " ", B42)</f>
-        <v>TL431AQDBZR SOT-23</v>
+        <v>TL431AQDBZR SOT23</v>
       </c>
       <c r="D42" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E42" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F42" t="s">
-        <v>279</v>
+        <v>181</v>
       </c>
       <c r="G42" t="s">
         <v>8</v>
